--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 78M D100 Spring 2024 24G302I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 78M D100 Spring 2024 24G302I13 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Erie\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1AA854-05AF-4F9E-B584-C72B27A1267D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E064AE56-1043-462C-9E27-929781524DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1830735D-C4F9-4134-A962-8D5EFCA43BA5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1830735D-C4F9-4134-A962-8D5EFCA43BA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId2"/>
+    <pivotCache cacheId="8" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4698,7 +4698,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63E3E2A6-F1E1-4DE6-8959-1BC59AD612FD}" name="PivotTable2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63E3E2A6-F1E1-4DE6-8959-1BC59AD612FD}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U1:Y15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -5137,21 +5137,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89566B47-F8F8-4D4F-BA66-EE0FC83F7481}">
   <dimension ref="A1:Y207"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="4" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="W21" s="13"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="W22" s="13"/>
     </row>
-    <row r="23" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="W23" s="13"/>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7054,7 +7054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -7372,7 +7372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -7690,7 +7690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8002,13 +8002,13 @@
         <v>0.82099999999999995</v>
       </c>
       <c r="P49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -9433,13 +9433,13 @@
         <v>0.86099999999999999</v>
       </c>
       <c r="P76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -10711,7 +10711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -11188,7 +11188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -11294,7 +11294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -11559,7 +11559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -11665,7 +11665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -11877,7 +11877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -11930,7 +11930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -12248,7 +12248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -12301,7 +12301,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -12354,7 +12354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -12566,7 +12566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -12937,7 +12937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -12990,7 +12990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13043,7 +13043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -13149,7 +13149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -13308,7 +13308,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -13361,7 +13361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -13414,7 +13414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -13573,7 +13573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -13679,7 +13679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -13732,7 +13732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -13832,13 +13832,13 @@
         <v>0.80800000000000005</v>
       </c>
       <c r="P159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q159">
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -13891,7 +13891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14044,13 +14044,13 @@
         <v>0.79600000000000004</v>
       </c>
       <c r="P163" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q163">
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14103,7 +14103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -14156,7 +14156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -14368,7 +14368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -14421,7 +14421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -14474,7 +14474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -14511,23 +14511,23 @@
       <c r="L172" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M172" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N172" s="2" t="s">
-        <v>33</v>
+      <c r="M172" t="s">
+        <v>36</v>
+      </c>
+      <c r="N172" t="s">
+        <v>37</v>
       </c>
       <c r="O172">
         <v>0.74399999999999999</v>
       </c>
       <c r="P172" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q172">
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -14580,7 +14580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -14633,7 +14633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -14951,7 +14951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15004,7 +15004,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15057,7 +15057,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15110,7 +15110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -15163,7 +15163,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -15216,7 +15216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -15269,7 +15269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -15375,7 +15375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -15534,7 +15534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -15587,7 +15587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -15640,7 +15640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -15693,7 +15693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -15746,7 +15746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -15799,7 +15799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -15852,7 +15852,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -15905,7 +15905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
         <v>18</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
         <v>18</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
         <v>18</v>
       </c>
@@ -16064,7 +16064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
         <v>18</v>
       </c>
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
         <v>18</v>
       </c>
@@ -16170,7 +16170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
         <v>18</v>
       </c>
@@ -16223,7 +16223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>18</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
         <v>18</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
         <v>18</v>
       </c>
